--- a/Tables/aov_fitness_all_table.xlsx
+++ b/Tables/aov_fitness_all_table.xlsx
@@ -394,17 +394,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>0.756</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>1.794</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.183</t>
         </is>
       </c>
     </row>
@@ -421,7 +421,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>52.491</t>
+          <t>47.216</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -492,17 +492,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.122</t>
+          <t>1.909</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.212</t>
+          <t>2.603</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.109</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>73.983</t>
+          <t>82.118</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
